--- a/fields/Field - Match 1.xlsx
+++ b/fields/Field - Match 1.xlsx
@@ -21,6 +21,23 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+  <si>
+    <t>Corner 1</t>
+  </si>
+  <si>
+    <t>Corner 2</t>
+  </si>
+  <si>
+    <t>Corner 3</t>
+  </si>
+  <si>
+    <t>Corner 4</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -336,10 +353,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:C4"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1">
         <v>-23.193470000000001</v>
       </c>
@@ -347,7 +367,10 @@
         <v>-47.292786999999997</v>
       </c>
     </row>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
       <c r="B2">
         <v>-23.193300000000001</v>
       </c>
@@ -355,7 +378,10 @@
         <v>-47.292155000000001</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
       <c r="B3">
         <v>-23.192564000000001</v>
       </c>
@@ -363,7 +389,10 @@
         <v>-47.293070999999998</v>
       </c>
     </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
       <c r="B4">
         <v>-23.192398000000001</v>
       </c>
